--- a/MinMax/scripts/comparison/violations_comparison_table_57_1.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_57_1.xlsx
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>5.03230512549635E-05</v>
+        <v>5.029900057706982E-05</v>
       </c>
       <c r="C12">
-        <v>5.032095941714942E-05</v>
+        <v>5.029795283917338E-05</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.002868413925170898</v>
+        <v>0.002867043018341064</v>
       </c>
       <c r="C13">
-        <v>0.002868294715881348</v>
+        <v>0.002866983413696289</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>2.093820421242171E-08</v>
+        <v>1.606262211336186E-08</v>
       </c>
       <c r="C16">
-        <v>1.468460111404117E-08</v>
+        <v>1.803758819692349E-08</v>
       </c>
       <c r="D16">
-        <v>1.422270657921998E-06</v>
+        <v>1.422307377652032E-06</v>
       </c>
       <c r="E16">
-        <v>1.24743459592837E-06</v>
+        <v>1.247429850081971E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>3.692322182119396E-07</v>
+        <v>2.520404899974487E-07</v>
       </c>
       <c r="C17">
-        <v>1.41013040834565E-07</v>
+        <v>1.608604921254452E-07</v>
       </c>
       <c r="D17">
-        <v>5.524820284115636E-06</v>
+        <v>5.524820153368637E-06</v>
       </c>
       <c r="E17">
-        <v>5.247082956648842E-06</v>
+        <v>5.247082754067378E-06</v>
       </c>
     </row>
   </sheetData>
